--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>3.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.46</v>
+        <v>3.57</v>
       </c>
       <c r="R21" t="n">
-        <v>6.81</v>
+        <v>2.14</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.34</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>4.46</v>
       </c>
       <c r="R13" t="n">
-        <v>2.14</v>
+        <v>6.81</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.77</v>
+        <v>3.57</v>
       </c>
       <c r="R14" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6.88</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>6.88</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G50" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.57</v>
+        <v>3.77</v>
       </c>
       <c r="R14" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>6.88</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S38" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G50" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R9" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="R14" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.57</v>
+        <v>3.77</v>
       </c>
       <c r="R16" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S37" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G50" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R9" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R10" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R37" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S38" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G50" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S37" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G50" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.48</v>
+        <v>3.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.46</v>
+        <v>3.57</v>
       </c>
       <c r="R12" t="n">
-        <v>6.81</v>
+        <v>2.14</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.34</v>
+        <v>1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.57</v>
+        <v>4.46</v>
       </c>
       <c r="R16" t="n">
-        <v>2.14</v>
+        <v>6.81</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="R21" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R9" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.53</v>
+        <v>4.46</v>
       </c>
       <c r="R21" t="n">
-        <v>2.98</v>
+        <v>6.81</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R37" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S38" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G50" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.57</v>
+        <v>3.77</v>
       </c>
       <c r="R23" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S37" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI50"/>
+  <dimension ref="A1:BI51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>3.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.46</v>
+        <v>3.57</v>
       </c>
       <c r="R21" t="n">
-        <v>6.81</v>
+        <v>2.14</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7643,27 +7643,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46167.65625</v>
+        <v>46167.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="R39" t="n">
-        <v>3.09</v>
+        <v>2.69</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46167.66666666666</v>
+        <v>46167.65625</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46167.79166666666</v>
+        <v>46167.66666666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46167.83333333334</v>
+        <v>46167.79166666666</v>
       </c>
     </row>
     <row r="42">
@@ -9022,27 +9022,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46167.875</v>
+        <v>46167.83333333334</v>
       </c>
     </row>
     <row r="45">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,6 +10392,203 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
+        <v>46167.875</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" s="3" t="n">
         <v>46167.875</v>
       </c>
     </row>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R18" t="n">
-        <v>6.81</v>
+        <v>2.34</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.34</v>
+        <v>3.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="R22" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="S36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S38" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R39" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R13" t="n">
-        <v>6.81</v>
+        <v>2.34</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>3.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="R15" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.34</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="R15" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R9" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R10" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R9" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.53</v>
+        <v>4.46</v>
       </c>
       <c r="R14" t="n">
-        <v>2.98</v>
+        <v>6.81</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.98</v>
+        <v>2.41</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R29" t="n">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="S35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S39" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R9" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R10" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.48</v>
+        <v>3.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.46</v>
+        <v>3.57</v>
       </c>
       <c r="R14" t="n">
-        <v>6.81</v>
+        <v>2.14</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G50" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>3.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.77</v>
+        <v>3.57</v>
       </c>
       <c r="R15" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S38" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R39" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI51"/>
+  <dimension ref="A1:BI53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46167.48958333334</v>
+        <v>46167.47916666666</v>
       </c>
     </row>
     <row r="10">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46167.48958333334</v>
+        <v>46167.47916666666</v>
       </c>
     </row>
     <row r="11">
@@ -2521,27 +2521,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46167.5</v>
+        <v>46167.48958333334</v>
       </c>
     </row>
     <row r="12">
@@ -2718,27 +2718,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46167.5</v>
+        <v>46167.48958333334</v>
       </c>
     </row>
     <row r="13">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.34</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.98</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="R18" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46167.52083333334</v>
+        <v>46167.5</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46167.54166666666</v>
+        <v>46167.5</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46167.55208333334</v>
+        <v>46167.5</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46167.58333333334</v>
+        <v>46167.5</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46167.58333333334</v>
+        <v>46167.52083333334</v>
       </c>
     </row>
     <row r="30">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46167.58333333334</v>
+        <v>46167.54166666666</v>
       </c>
     </row>
     <row r="31">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46167.58333333334</v>
+        <v>46167.55208333334</v>
       </c>
     </row>
     <row r="32">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.41</v>
+        <v>2.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46167.58680555555</v>
+        <v>46167.58333333334</v>
       </c>
     </row>
     <row r="34">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46167.59375</v>
+        <v>46167.58333333334</v>
       </c>
     </row>
     <row r="35">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46167.60416666666</v>
+        <v>46167.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -7446,27 +7446,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="R36" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="S36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46167.60416666666</v>
+        <v>46167.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -7643,27 +7643,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="R37" t="n">
-        <v>2.9</v>
+        <v>4.74</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46167.60416666666</v>
+        <v>46167.58680555555</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.51</v>
+        <v>1.87</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.32</v>
+        <v>3.79</v>
       </c>
       <c r="R38" t="n">
-        <v>2.69</v>
+        <v>4.05</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46167.65625</v>
+        <v>46167.59375</v>
       </c>
     </row>
     <row r="39">
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>6.88</v>
+        <v>1.73</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="S39" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46167.65625</v>
+        <v>46167.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -8234,27 +8234,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46167.66666666666</v>
+        <v>46167.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,27 +8431,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46167.79166666666</v>
+        <v>46167.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>6.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46167.83333333334</v>
+        <v>46167.65625</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.72</v>
+        <v>2.51</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="R43" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46167.83333333334</v>
+        <v>46167.65625</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46167.83333333334</v>
+        <v>46167.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46167.875</v>
+        <v>46167.79166666666</v>
       </c>
     </row>
     <row r="46">
@@ -9416,27 +9416,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46167.875</v>
+        <v>46167.83333333334</v>
       </c>
     </row>
     <row r="47">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46167.875</v>
+        <v>46167.83333333334</v>
       </c>
     </row>
     <row r="48">
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46167.875</v>
+        <v>46167.83333333334</v>
       </c>
     </row>
     <row r="49">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10589,6 +10589,400 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
+        <v>46167.875</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="3" t="n">
+        <v>46167.875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Borac Banja Luka</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Posusje</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" s="3" t="n">
         <v>46167.875</v>
       </c>
     </row>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.34</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.57</v>
+        <v>4.46</v>
       </c>
       <c r="R15" t="n">
-        <v>2.14</v>
+        <v>6.81</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,17 +5722,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.98</v>
+        <v>2.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R32" t="n">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.41</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S42" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R43" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,17 +5722,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>2.41</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R36" t="n">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R39" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>1.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.28</v>
+        <v>6.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R12" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R27" t="n">
         <v>2.34</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.98</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="R28" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.41</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R42" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S43" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="R5" t="n">
-        <v>5.97</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.18</v>
+        <v>9.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="R7" t="n">
-        <v>12.2</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>5.97</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R11" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,17 +4934,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,17 +5328,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>1.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="R36" t="n">
-        <v>2.29</v>
+        <v>7.55</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.18</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.2</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>1.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>6.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>5.97</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>9.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R8" t="n">
-        <v>5.97</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>3.53</v>
       </c>
       <c r="R13" t="n">
-        <v>4.03</v>
+        <v>2.98</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.53</v>
+        <v>2.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>3.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="R15" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,17 +3752,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4153,10 +4153,10 @@
         <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.45</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.66</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>4.46</v>
       </c>
       <c r="R21" t="n">
-        <v>3.23</v>
+        <v>6.81</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.86</v>
+        <v>3.72</v>
       </c>
       <c r="R22" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.46</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>6.81</v>
+        <v>3.23</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,17 +5328,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.34</v>
+        <v>1.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.57</v>
+        <v>4.1</v>
       </c>
       <c r="R26" t="n">
-        <v>2.14</v>
+        <v>4.03</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.83</v>
+        <v>3.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.77</v>
+        <v>3.66</v>
       </c>
       <c r="R27" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.98</v>
+        <v>2.41</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R34" t="n">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.34</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>7.55</v>
+        <v>2.29</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="S41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S42" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R43" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.53</v>
+        <v>4.05</v>
       </c>
       <c r="R13" t="n">
-        <v>2.98</v>
+        <v>4.03</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.94</v>
+        <v>2.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,17 +3752,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.86</v>
+        <v>4.85</v>
       </c>
       <c r="R19" t="n">
-        <v>2.53</v>
+        <v>5.63</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="R20" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>3.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.46</v>
+        <v>3.66</v>
       </c>
       <c r="R21" t="n">
-        <v>6.81</v>
+        <v>1.96</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.53</v>
+        <v>2.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>2.41</v>
+        <v>3.23</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.05</v>
+        <v>4.46</v>
       </c>
       <c r="R24" t="n">
-        <v>4.03</v>
+        <v>6.81</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,17 +5328,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
       <c r="R27" t="n">
-        <v>1.96</v>
+        <v>2.53</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.45</v>
+        <v>2.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.85</v>
+        <v>3.77</v>
       </c>
       <c r="R28" t="n">
-        <v>5.63</v>
+        <v>2.34</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.41</v>
+        <v>2.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R39" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="S39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="Q40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU40" t="n">
         <v>3.25</v>
       </c>
-      <c r="R40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>1.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>6.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.18</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.2</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.53</v>
+        <v>2.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.94</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>4.46</v>
       </c>
       <c r="R15" t="n">
-        <v>2.27</v>
+        <v>6.81</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="R16" t="n">
-        <v>4.03</v>
+        <v>2.34</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.54</v>
+        <v>4.85</v>
       </c>
       <c r="R17" t="n">
-        <v>2.69</v>
+        <v>5.63</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.34</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.57</v>
+        <v>4.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.14</v>
+        <v>4.03</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.85</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>5.63</v>
+        <v>4.03</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.53</v>
+        <v>3.72</v>
       </c>
       <c r="R20" t="n">
-        <v>2.98</v>
+        <v>2.41</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.66</v>
+        <v>3.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.96</v>
+        <v>2.69</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,17 +5328,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.86</v>
+        <v>3.53</v>
       </c>
       <c r="R27" t="n">
-        <v>2.53</v>
+        <v>2.98</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="R28" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.98</v>
+        <v>1.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="R34" t="n">
-        <v>2.29</v>
+        <v>7.55</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R42" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S43" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.18</v>
+        <v>9.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="R5" t="n">
-        <v>12.2</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="R7" t="n">
-        <v>5.97</v>
+        <v>12.2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>5.97</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.46</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
-        <v>6.81</v>
+        <v>2.69</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="R16" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.53</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="R20" t="n">
-        <v>2.41</v>
+        <v>4.03</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.54</v>
+        <v>3.77</v>
       </c>
       <c r="R21" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>4.46</v>
       </c>
       <c r="R22" t="n">
-        <v>3.23</v>
+        <v>6.81</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.45</v>
+        <v>2.01</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.96</v>
+        <v>3.23</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.34</v>
+        <v>2.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="R25" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.34</v>
+        <v>1.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.53</v>
+        <v>4.85</v>
       </c>
       <c r="R27" t="n">
-        <v>2.98</v>
+        <v>5.63</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.34</v>
+        <v>2.41</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.7</v>
+        <v>3.54</v>
       </c>
       <c r="R34" t="n">
-        <v>7.55</v>
+        <v>2.67</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.41</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S42" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R43" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>9.4</v>
+        <v>1.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.18</v>
+        <v>9.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="R7" t="n">
-        <v>12.2</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.69</v>
+        <v>3.23</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="R19" t="n">
-        <v>4.03</v>
+        <v>2.69</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>4.03</v>
+        <v>2.53</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="R21" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>6.81</v>
+        <v>2.34</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="R23" t="n">
-        <v>3.23</v>
+        <v>4.03</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.34</v>
+        <v>1.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.57</v>
+        <v>4.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2.14</v>
+        <v>5.63</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2.98</v>
+        <v>2.27</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.45</v>
+        <v>1.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.66</v>
+        <v>4.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.96</v>
+        <v>4.03</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,17 +5722,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.86</v>
+        <v>3.66</v>
       </c>
       <c r="R28" t="n">
-        <v>2.53</v>
+        <v>1.96</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.34</v>
+        <v>2.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.7</v>
+        <v>3.54</v>
       </c>
       <c r="R33" t="n">
-        <v>7.55</v>
+        <v>2.67</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.41</v>
+        <v>2.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU39" t="n">
         <v>3.25</v>
       </c>
-      <c r="R39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="S40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R41" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.18</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.2</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>9.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>5.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>5.97</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="R8" t="n">
-        <v>5.97</v>
+        <v>12.2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="R12" t="n">
-        <v>2.91</v>
+        <v>2.32</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="R15" t="n">
-        <v>3.23</v>
+        <v>1.96</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.53</v>
+        <v>4.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.98</v>
+        <v>4.03</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.54</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.86</v>
+        <v>3.53</v>
       </c>
       <c r="R20" t="n">
-        <v>2.53</v>
+        <v>2.98</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R21" t="n">
         <v>2.53</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.41</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="R22" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.05</v>
+        <v>4.46</v>
       </c>
       <c r="R23" t="n">
-        <v>4.03</v>
+        <v>6.81</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.45</v>
+        <v>3.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.85</v>
+        <v>3.57</v>
       </c>
       <c r="R24" t="n">
-        <v>5.63</v>
+        <v>2.14</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>4.03</v>
+        <v>2.27</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,17 +5722,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.66</v>
+        <v>3.54</v>
       </c>
       <c r="R28" t="n">
-        <v>1.96</v>
+        <v>2.69</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.98</v>
+        <v>2.41</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R34" t="n">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="S39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.76</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>5.45</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.49</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,52 +1276,52 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>5.97</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1416,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1431,40 +1431,40 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.63</v>
+        <v>2.06</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>9.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.6</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,22 +1786,22 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="R7" t="n">
-        <v>5.97</v>
+        <v>12.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1810,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1825,40 +1825,40 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.18</v>
+        <v>9.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="R8" t="n">
-        <v>12.2</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2022,40 +2022,40 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,83 +2964,83 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3049,52 +3049,52 @@
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>4.03</v>
+        <v>2.88</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,52 +3246,52 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
       <c r="R15" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3446,13 +3446,13 @@
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
@@ -3461,34 +3461,34 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>4.35</v>
       </c>
       <c r="R16" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,52 +3640,52 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3840,13 +3840,13 @@
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
@@ -3855,34 +3855,34 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
-        <v>4.03</v>
+        <v>2.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW21" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.41</v>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4822,52 +4822,52 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,97 +4938,97 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
         <v>1.48</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AU23" t="n">
         <v>0</v>
@@ -5037,34 +5037,34 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5174,40 +5174,40 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
@@ -5431,34 +5431,34 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.85</v>
+        <v>3.85</v>
       </c>
       <c r="R27" t="n">
-        <v>5.63</v>
+        <v>3.55</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5810,13 +5810,13 @@
         <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
@@ -5825,34 +5825,34 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.54</v>
+        <v>3.77</v>
       </c>
       <c r="R28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL28" t="n">
         <v>2.69</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6007,13 +6007,13 @@
         <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AU28" t="n">
         <v>0</v>
@@ -6022,34 +6022,34 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R39" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R42" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S43" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>1.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>6.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1628,40 +1628,40 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.18</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>12.2</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
-        <v>1.52</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>8.5</v>
+        <v>3.07</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X7" t="n">
-        <v>1.91</v>
+        <v>2.94</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.2</v>
+        <v>6.85</v>
       </c>
       <c r="AJ7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
         <v>1.27</v>
       </c>
-      <c r="AK7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS11" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="R12" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="S13" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
         <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="V13" t="n">
         <v>1.3</v>
@@ -2992,16 +2992,16 @@
         <v>3.16</v>
       </c>
       <c r="X13" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>6</v>
+        <v>5.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
@@ -3010,37 +3010,37 @@
         <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3049,52 +3049,52 @@
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,80 +3165,80 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
@@ -3246,52 +3246,52 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3446,13 +3446,13 @@
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
@@ -3461,34 +3461,34 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="R16" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="X16" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AM16" t="n">
         <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,52 +3640,52 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,83 +3752,83 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3840,13 +3840,13 @@
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
@@ -3855,34 +3855,34 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,94 +3953,94 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="U18" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="X18" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.64</v>
       </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AF18" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AS18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AT18" t="n">
         <v>2.1</v>
@@ -4049,37 +4049,37 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,52 +4231,52 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU19" t="n">
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,52 +4428,52 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.46</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>6.5</v>
+        <v>2.11</v>
       </c>
       <c r="S21" t="n">
-        <v>1.85</v>
+        <v>3.58</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z21" t="n">
         <v>6</v>
       </c>
-      <c r="V21" t="n">
+      <c r="AA21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.22</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.65</v>
+        <v>5.65</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="X22" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.35</v>
+        <v>3.84</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN22" t="n">
         <v>2.6</v>
       </c>
-      <c r="AH22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC22" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5022,13 +5022,13 @@
         <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
         <v>0</v>
@@ -5037,34 +5037,34 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.94</v>
+        <v>1.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="R24" t="n">
-        <v>2.27</v>
+        <v>6.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,97 +5332,97 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="T25" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="V25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.25</v>
       </c>
-      <c r="W25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK25" t="n">
+      <c r="AN25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS25" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AT25" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
@@ -5431,34 +5431,34 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="AX25" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AZ25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BE25" t="n">
         <v>2.25</v>
       </c>
-      <c r="BA25" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,83 +5525,83 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5610,52 +5610,52 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU26" t="n">
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.34</v>
+        <v>2.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>7.55</v>
+        <v>2.29</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -8099,124 +8099,124 @@
         <v>2.9</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8493,40 +8493,40 @@
         <v>4.5</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE41" t="n">
         <v>2.03</v>
@@ -8535,82 +8535,82 @@
         <v>1.78</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S42" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R43" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.45</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>5.5</v>
+        <v>2.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
-        <v>3.01</v>
+        <v>2.44</v>
       </c>
       <c r="X2" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="Y2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN2" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.76</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>5.45</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>3.01</v>
       </c>
       <c r="X3" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.33</v>
+        <v>3.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>9.199999999999999</v>
+        <v>6.35</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>5.97</v>
+        <v>2.62</v>
       </c>
       <c r="S5" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>5.3</v>
+        <v>3.07</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X5" t="n">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.5</v>
+        <v>6.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
         <v>1.93</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC5" t="n">
         <v>2.25</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.18</v>
       </c>
-      <c r="Q6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AD6" t="n">
-        <v>5.25</v>
+        <v>3.95</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.62</v>
+        <v>1.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>12.2</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>1.52</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.07</v>
+        <v>8.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.94</v>
+        <v>1.91</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.85</v>
+        <v>3.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL7" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL7" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.47</v>
+        <v>3.7</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>2.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="X11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
         <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
         <v>1.85</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="AS11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC11" t="n">
         <v>2.3</v>
       </c>
-      <c r="AT11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX11" t="n">
+      <c r="BD11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.53</v>
       </c>
-      <c r="AY11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="X12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB12" t="n">
         <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.17</v>
+        <v>1.84</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="AW12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.6</v>
       </c>
-      <c r="AX12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="S13" t="n">
         <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM13" t="n">
         <v>1.3</v>
       </c>
-      <c r="W13" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AN13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.94</v>
+        <v>1.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="R14" t="n">
-        <v>2.27</v>
+        <v>5.65</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.9</v>
+        <v>2.44</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
@@ -3264,34 +3264,34 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,52 +3443,52 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>3.95</v>
+        <v>6.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
         <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="X16" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,52 +3640,52 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,83 +3752,83 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3840,13 +3840,13 @@
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
@@ -3855,34 +3855,34 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,83 +3949,83 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4037,13 +4037,13 @@
         <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
@@ -4052,34 +4052,34 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="X19" t="n">
-        <v>2.56</v>
+        <v>2.17</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AK19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN19" t="n">
         <v>2</v>
       </c>
-      <c r="AG19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM19" t="n">
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>3.68</v>
+        <v>3.16</v>
       </c>
       <c r="X20" t="n">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AB20" t="n">
         <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM20" t="n">
+      <c r="AN20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,80 +4544,80 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="Q21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG21" t="n">
         <v>3.4</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="AH21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN21" t="n">
         <v>1.3</v>
       </c>
-      <c r="W21" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
@@ -4625,52 +4625,52 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,80 +4741,80 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R22" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI22" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="AJ22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN22" t="n">
         <v>1.36</v>
       </c>
-      <c r="AK22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
@@ -4822,52 +4822,52 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.38</v>
+        <v>1.96</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.15</v>
+        <v>1.94</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="R24" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="S24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN24" t="n">
         <v>1.85</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD24" t="n">
         <v>5</v>
       </c>
-      <c r="AA24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL24" t="n">
+      <c r="BE24" t="n">
         <v>2.05</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
+      <c r="BF24" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.63</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.8</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="X25" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.91</v>
+        <v>2.57</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AM25" t="n">
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.4</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.77</v>
+        <v>2.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.35</v>
+        <v>3.77</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="V26" t="n">
         <v>1.23</v>
       </c>
       <c r="W26" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="X26" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5610,52 +5610,52 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5810,13 +5810,13 @@
         <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
@@ -5825,34 +5825,34 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="R28" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="T28" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
         <v>1.23</v>
       </c>
       <c r="W28" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="X28" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT28" t="n">
         <v>2.25</v>
       </c>
-      <c r="AH28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AJ28" t="n">
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF28" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R42" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S43" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>9.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="U5" t="n">
-        <v>3.07</v>
+        <v>1.61</v>
       </c>
       <c r="V5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.94</v>
+        <v>1.92</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1.98</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ5" t="n">
+      <c r="AM5" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AN5" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="R6" t="n">
-        <v>5.97</v>
+        <v>12.2</v>
       </c>
       <c r="S6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.95</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AL6" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.18</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>12.2</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
-        <v>1.52</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>8.5</v>
+        <v>3.07</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X7" t="n">
-        <v>1.91</v>
+        <v>2.94</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.2</v>
+        <v>6.85</v>
       </c>
       <c r="AJ7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
         <v>1.27</v>
       </c>
-      <c r="AK7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>5.97</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>5.3</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2022,40 +2022,40 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.04</v>
+        <v>2.25</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="R13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.88</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.25</v>
       </c>
-      <c r="U13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD13" t="n">
         <v>5</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM13" t="n">
+      <c r="BE13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>5.65</v>
+        <v>2.88</v>
       </c>
       <c r="S14" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT14" t="n">
         <v>2.7</v>
       </c>
-      <c r="U14" t="n">
-        <v>5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC14" t="n">
         <v>1.95</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BD14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,34 +3362,34 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>2.35</v>
+        <v>6.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="X15" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
         <v>5</v>
@@ -3398,97 +3398,97 @@
         <v>1.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AM15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.46</v>
+        <v>2.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>6.5</v>
+        <v>2.27</v>
       </c>
       <c r="S16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.43</v>
+        <v>3.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,52 +3640,52 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,83 +3752,83 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3840,13 +3840,13 @@
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
@@ -3855,34 +3855,34 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,83 +3949,83 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="R19" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="X19" t="n">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4234,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AU19" t="n">
         <v>0</v>
@@ -4249,34 +4249,34 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.43</v>
+        <v>3.15</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="R20" t="n">
-        <v>2.65</v>
+        <v>5.65</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="X20" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.35</v>
+        <v>3.84</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AG20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.6</v>
       </c>
-      <c r="AH20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ20" t="n">
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC20" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,52 +4625,52 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>3.16</v>
+        <v>3.68</v>
       </c>
       <c r="X22" t="n">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AB22" t="n">
         <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4825,49 +4825,49 @@
         <v>1.27</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AW22" t="n">
         <v>2.48</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5022,13 +5022,13 @@
         <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU23" t="n">
         <v>0</v>
@@ -5037,34 +5037,34 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,34 +5135,34 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="R24" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="S24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="U24" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Z24" t="n">
         <v>4.5</v>
@@ -5171,7 +5171,7 @@
         <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
         <v>1.14</v>
@@ -5183,16 +5183,16 @@
         <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
         <v>1.62</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.22</v>
@@ -5201,13 +5201,13 @@
         <v>1.44</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
         <v>1.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="BF24" t="n">
         <v>1.3</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="X25" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="AA25" t="n">
         <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,49 +5413,49 @@
         <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AX25" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.71</v>
+        <v>2.23</v>
       </c>
       <c r="BB25" t="n">
         <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BF25" t="n">
         <v>1.25</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5613,13 +5613,13 @@
         <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
         <v>0</v>
@@ -5628,34 +5628,34 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5810,13 +5810,13 @@
         <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
@@ -5825,34 +5825,34 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6004,52 +6004,52 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.34</v>
+        <v>2.41</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.7</v>
+        <v>3.54</v>
       </c>
       <c r="R36" t="n">
-        <v>7.55</v>
+        <v>2.67</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="S40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W40" t="n">
         <v>3.05</v>
       </c>
-      <c r="T40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W40" t="n">
-        <v>2.73</v>
-      </c>
       <c r="X40" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="Z40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="AE40" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL40" t="n">
         <v>2</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1.97</v>
       </c>
       <c r="AM40" t="n">
         <v>1.29</v>
       </c>
       <c r="AN40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX40" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.54</v>
       </c>
       <c r="AY40" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="BB40" t="n">
         <v>1.22</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="S41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.1</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U41" t="n">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="V41" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W41" t="n">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="X41" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AI41" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL41" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AM41" t="n">
         <v>1.29</v>
       </c>
       <c r="AN41" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AT41" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AY41" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="BB41" t="n">
         <v>1.22</v>
       </c>
       <c r="BC41" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.25</v>
+        <v>3.32</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="S42" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.51</v>
+        <v>6.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="R43" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,113 +801,113 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT2" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AU2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX2" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AY2" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W3" t="n">
-        <v>3.01</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="Q4" t="n">
         <v>3.74</v>
@@ -1207,7 +1207,7 @@
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U4" t="n">
         <v>2.7</v>
@@ -1216,28 +1216,28 @@
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="X4" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
         <v>5.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AE4" t="n">
         <v>1.57</v>
@@ -1246,40 +1246,40 @@
         <v>2.35</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
         <v>1.52</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AM4" t="n">
         <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AS4" t="n">
         <v>1.78</v>
@@ -1288,19 +1288,19 @@
         <v>2.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AX4" t="n">
         <v>1.91</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.96</v>
@@ -1309,10 +1309,10 @@
         <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BD4" t="n">
         <v>4.75</v>
@@ -1321,7 +1321,7 @@
         <v>1.95</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.18</v>
       </c>
-      <c r="Q6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AD6" t="n">
-        <v>5.25</v>
+        <v>3.95</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.62</v>
+        <v>1.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>12.2</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>1.52</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.07</v>
+        <v>8.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.94</v>
+        <v>1.91</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.85</v>
+        <v>3.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL7" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL7" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.47</v>
+        <v>3.7</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>5.97</v>
+        <v>2.62</v>
       </c>
       <c r="S8" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="U8" t="n">
-        <v>5.3</v>
+        <v>3.07</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X8" t="n">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.5</v>
+        <v>6.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
         <v>1.93</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC8" t="n">
         <v>2.25</v>
       </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2983,10 +2983,10 @@
         <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>3.58</v>
@@ -2995,37 +2995,37 @@
         <v>2.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH13" t="n">
         <v>1.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AJ13" t="n">
         <v>1.25</v>
@@ -3034,13 +3034,13 @@
         <v>1.41</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AM13" t="n">
         <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>3.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="U14" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="X14" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB14" t="n">
         <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.6</v>
+        <v>3.26</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BB14" t="n">
         <v>1.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,28 +3362,28 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>6.5</v>
+        <v>3.35</v>
       </c>
       <c r="S15" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="X15" t="n">
         <v>2.25</v>
@@ -3392,28 +3392,28 @@
         <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
         <v>1.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.6</v>
+        <v>4.72</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>2.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AH15" t="n">
         <v>1.5</v>
@@ -3425,67 +3425,67 @@
         <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AV15" t="n">
         <v>3.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BF15" t="n">
         <v>1.25</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.94</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="R16" t="n">
-        <v>2.27</v>
+        <v>5.7</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.68</v>
+        <v>2.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.25</v>
+        <v>2.81</v>
       </c>
       <c r="AJ16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.05</v>
       </c>
-      <c r="AK16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,137 +3752,137 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.35</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.25</v>
+        <v>3.03</v>
       </c>
       <c r="T18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.4</v>
       </c>
-      <c r="U18" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AI18" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.95</v>
+        <v>2.02</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>5.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4234,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
         <v>0</v>
@@ -4249,34 +4249,34 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>5.65</v>
+        <v>2.27</v>
       </c>
       <c r="S20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>6.5</v>
+        <v>3.05</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.44</v>
+        <v>1.9</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
@@ -4446,34 +4446,34 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>1.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.11</v>
+        <v>6.1</v>
       </c>
       <c r="S21" t="n">
-        <v>3.58</v>
+        <v>1.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="X21" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1.15</v>
       </c>
-      <c r="AK21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AN21" t="n">
-        <v>1.36</v>
+        <v>2.69</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.96</v>
+        <v>1.39</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.94</v>
+        <v>3.45</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,130 +4741,130 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="X22" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AD22" t="n">
         <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH22" t="n">
         <v>1.62</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
         <v>1.44</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BA22" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="BB22" t="n">
         <v>1.15</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BF22" t="n">
         <v>1.3</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
         <v>3.4</v>
       </c>
       <c r="R23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.1</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.15</v>
       </c>
       <c r="AK23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR23" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AS23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AX23" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.71</v>
+        <v>2.23</v>
       </c>
       <c r="BB23" t="n">
         <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BF23" t="n">
         <v>1.25</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,83 +5131,83 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
@@ -5234,34 +5234,34 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R25" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="U25" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>3.16</v>
+        <v>3.75</v>
       </c>
       <c r="X25" t="n">
-        <v>2.41</v>
+        <v>2.19</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AB25" t="n">
         <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AG25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL25" t="n">
         <v>2.6</v>
       </c>
-      <c r="AH25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AM25" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>2.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>3.55</v>
+        <v>2.19</v>
       </c>
       <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>2.25</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM27" t="n">
+      <c r="BA27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6523,13 +6523,13 @@
         <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6553,40 +6553,40 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6631,13 +6631,13 @@
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7222,13 +7222,13 @@
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="R35" t="n">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AE35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF35" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF35" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.54</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7580,52 +7580,52 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU36" t="n">
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Q37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U37" t="n">
         <v>4.6</v>
       </c>
-      <c r="R37" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7896,130 +7896,130 @@
         <v>1.87</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="R38" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="S40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T40" t="n">
         <v>2.1</v>
       </c>
-      <c r="T40" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U40" t="n">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="V40" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W40" t="n">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="X40" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AI40" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL40" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AM40" t="n">
         <v>1.29</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AT40" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AY40" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="BB40" t="n">
         <v>1.22</v>
       </c>
       <c r="BC40" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="S41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W41" t="n">
         <v>3.05</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W41" t="n">
-        <v>2.73</v>
-      </c>
       <c r="X41" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="Z41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="AE41" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL41" t="n">
         <v>2</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.97</v>
       </c>
       <c r="AM41" t="n">
         <v>1.29</v>
       </c>
       <c r="AN41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX41" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.54</v>
       </c>
       <c r="AY41" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="BB41" t="n">
         <v>1.22</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W42" t="n">
         <v>2.69</v>
       </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>6.88</v>
+        <v>7.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
         <v>7.56</v>
       </c>
       <c r="T43" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V43" t="n">
         <v>1.33</v>
@@ -8902,43 +8902,43 @@
         <v>3.2</v>
       </c>
       <c r="X43" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.45</v>
+        <v>5.9</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC43" t="n">
         <v>1.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AE43" t="n">
         <v>1.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AI43" t="n">
         <v>5.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK43" t="n">
         <v>2</v>
@@ -8950,58 +8950,58 @@
         <v>2.8</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.6</v>
+        <v>6.44</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BB43" t="n">
         <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="BF43" t="n">
         <v>1.16</v>
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10463,13 +10463,13 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -10478,10 +10478,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -10493,40 +10493,40 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10571,13 +10571,13 @@
         <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD51" t="n">
         <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF51" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G53" t="n">

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>4.9</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U2" t="n">
-        <v>5.8</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AM2" t="n">
         <v>1.33</v>
       </c>
-      <c r="W2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AN2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW2" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AX2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,113 +998,113 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AU3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX3" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>1.18</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>5.97</v>
+        <v>2.62</v>
       </c>
       <c r="S6" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>5.3</v>
+        <v>3.07</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X6" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.95</v>
+        <v>2.99</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.5</v>
+        <v>6.85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
         <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC6" t="n">
         <v>2.25</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.62</v>
+        <v>5.97</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
-        <v>3.07</v>
+        <v>5.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.94</v>
+        <v>2.32</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.85</v>
+        <v>4.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL8" t="n">
         <v>1.93</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.47</v>
+        <v>2.25</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="X11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB11" t="n">
         <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AL11" t="n">
         <v>1.85</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.17</v>
+        <v>1.84</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="AW11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.6</v>
       </c>
-      <c r="AX11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="X12" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
         <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
         <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="AS12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC12" t="n">
         <v>2.3</v>
       </c>
-      <c r="AT12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX12" t="n">
+      <c r="BD12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.53</v>
       </c>
-      <c r="AY12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="X13" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA13" t="n">
         <v>2.23</v>
       </c>
-      <c r="AH13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="BB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,137 +3161,137 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>3.35</v>
+        <v>2.27</v>
       </c>
       <c r="S15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.72</v>
+        <v>3.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.39</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>5.7</v>
+        <v>2.46</v>
       </c>
       <c r="S16" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
         <v>1.17</v>
@@ -3583,109 +3583,109 @@
         <v>4.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AB16" t="n">
         <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX16" t="n">
         <v>1.87</v>
       </c>
-      <c r="AI16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AY16" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>2.46</v>
+        <v>3.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.17</v>
       </c>
-      <c r="W17" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AD17" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI17" t="n">
         <v>4.2</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AM17" t="n">
         <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.97</v>
+        <v>4.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.98</v>
+        <v>2.95</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>6.1</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
-        <v>1.89</v>
+        <v>3.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>5.5</v>
+        <v>2.51</v>
       </c>
       <c r="V21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="X21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL21" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2</v>
-      </c>
       <c r="AM21" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.69</v>
+        <v>1.36</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.22</v>
+        <v>4.97</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.07</v>
+        <v>3.26</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="AX21" t="n">
         <v>1.87</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.45</v>
+        <v>1.94</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>2.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>3.7</v>
+        <v>2.19</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>4.25</v>
+        <v>2.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="X22" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="Z22" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD22" t="n">
         <v>4.6</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AE22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.15</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE22" t="n">
+      <c r="AK22" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AL22" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="AU22" t="n">
         <v>4.39</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R23" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>3.16</v>
+        <v>3.68</v>
       </c>
       <c r="X23" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="AE23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC23" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4.33</v>
+        <v>5.45</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,37 +5332,37 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.82</v>
+        <v>2.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="R25" t="n">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="S25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.32</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.41</v>
-      </c>
       <c r="U25" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="V25" t="n">
         <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="X25" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
         <v>1.14</v>
@@ -5371,19 +5371,19 @@
         <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="n">
         <v>1.62</v>
@@ -5392,58 +5392,58 @@
         <v>3.7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="BB25" t="n">
         <v>1.15</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,130 +5726,130 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.95</v>
+        <v>1.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>2.19</v>
+        <v>6.1</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>1.89</v>
       </c>
       <c r="T27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.38</v>
       </c>
-      <c r="U27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="AG27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AN27" t="n">
-        <v>1.36</v>
+        <v>2.69</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.39</v>
+        <v>4.22</v>
       </c>
       <c r="AV27" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AX27" t="n">
         <v>1.87</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.25</v>
+        <v>1.39</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.71</v>
+        <v>3.45</v>
       </c>
       <c r="BB27" t="n">
         <v>1.18</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="BD27" t="n">
         <v>4.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BF27" t="n">
         <v>1.25</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>1.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="R28" t="n">
-        <v>3.04</v>
+        <v>3.55</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="T28" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="U28" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="V28" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="X28" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AM28" t="n">
         <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.22</v>
+        <v>5.44</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.87</v>
+        <v>2.51</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,52 +6792,52 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7222,13 +7222,13 @@
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.8</v>
+        <v>1.34</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.34</v>
+        <v>4.7</v>
       </c>
       <c r="R35" t="n">
-        <v>2.42</v>
+        <v>7.55</v>
       </c>
       <c r="S35" t="n">
-        <v>3.25</v>
+        <v>1.78</v>
       </c>
       <c r="T35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
         <v>2.1</v>
       </c>
-      <c r="U35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.53</v>
-      </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Z35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM35" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AN35" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,76 +7499,76 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="R36" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="S36" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
         <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V36" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W36" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X36" t="n">
         <v>2.53</v>
       </c>
-      <c r="X36" t="n">
-        <v>3.2</v>
-      </c>
       <c r="Y36" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AC36" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.12</v>
+        <v>3.52</v>
       </c>
       <c r="AE36" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AH36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM36" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.33</v>
       </c>
       <c r="AN36" t="n">
         <v>1.4</v>
@@ -7577,55 +7577,55 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AW36" t="n">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="AX36" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="BB36" t="n">
         <v>1.22</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.66</v>
+        <v>3.96</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R39" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.9</v>
-      </c>
       <c r="S39" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T39" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN39" t="n">
         <v>1.55</v>
       </c>
-      <c r="W39" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AF39" t="n">
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE39" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF39" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="Q40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S40" t="n">
         <v>3.3</v>
       </c>
-      <c r="R40" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.05</v>
-      </c>
       <c r="T40" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>3.58</v>
+        <v>4.13</v>
       </c>
       <c r="V40" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="W40" t="n">
-        <v>2.73</v>
+        <v>2.27</v>
       </c>
       <c r="X40" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
         <v>8</v>
       </c>
       <c r="AA40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC40" t="n">
+      <c r="AK40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BB40" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD40" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN40" t="n">
+      <c r="BC40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE40" t="n">
         <v>1.53</v>
       </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="S41" t="n">
         <v>2.1</v>
@@ -8499,10 +8499,10 @@
         <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="V41" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
         <v>3.05</v>
@@ -8523,37 +8523,37 @@
         <v>1.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AD41" t="n">
         <v>3.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AH41" t="n">
         <v>1.36</v>
       </c>
       <c r="AI41" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AL41" t="n">
         <v>2</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AN41" t="n">
         <v>2.1</v>
@@ -8601,7 +8601,7 @@
         <v>1.22</v>
       </c>
       <c r="BC41" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BD41" t="n">
         <v>3.9</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.4</v>
+        <v>7.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>4.31</v>
       </c>
       <c r="R42" t="n">
-        <v>2.71</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>7.56</v>
       </c>
       <c r="T42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF42" t="n">
         <v>2</v>
       </c>
-      <c r="U42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG42" t="n">
-        <v>3.44</v>
+        <v>2.7</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AI42" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.48</v>
+        <v>1.81</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.91</v>
+        <v>3.08</v>
       </c>
       <c r="AU42" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.07</v>
+        <v>2.41</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.66</v>
+        <v>6.44</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.4</v>
+        <v>1.23</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>7.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.31</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="S43" t="n">
-        <v>7.56</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="V43" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W43" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD43" t="n">
         <v>3.2</v>
       </c>
-      <c r="X43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD43" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AI43" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AM43" t="n">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.81</v>
+        <v>2.48</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.08</v>
+        <v>3.91</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.34</v>
+        <v>2.77</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AZ43" t="n">
-        <v>6.44</v>
+        <v>1.66</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.23</v>
+        <v>2.4</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10069,19 +10069,19 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -10099,22 +10099,22 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -10123,16 +10123,16 @@
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10177,13 +10177,13 @@
         <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD49" t="n">
         <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10463,13 +10463,13 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -10478,10 +10478,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -10493,40 +10493,40 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10571,13 +10571,13 @@
         <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD51" t="n">
         <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10660,13 +10660,13 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -10690,40 +10690,40 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10768,13 +10768,13 @@
         <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD52" t="n">
         <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10857,19 +10857,19 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -10887,22 +10887,22 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -10911,16 +10911,16 @@
         <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10965,13 +10965,13 @@
         <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD53" t="n">
         <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF53" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,113 +801,113 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT2" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AU2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX2" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>1.18</v>
       </c>
-      <c r="AY2" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>3.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>4.9</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U3" t="n">
-        <v>5.8</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1.33</v>
       </c>
-      <c r="W3" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AN3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW3" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AX3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.85</v>
+        <v>4.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL6" t="n">
         <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>5.97</v>
+        <v>2.62</v>
       </c>
       <c r="S8" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>5.3</v>
+        <v>3.07</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X8" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.95</v>
+        <v>2.99</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.5</v>
+        <v>6.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
         <v>1.93</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AN8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC8" t="n">
         <v>2.25</v>
       </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2971,130 +2971,130 @@
         <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="S13" t="n">
         <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="X13" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC13" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,137 +3161,137 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R15" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK15" t="n">
+      <c r="AR15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BA15" t="n">
         <v>1.71</v>
       </c>
-      <c r="AL15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.88</v>
+        <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.1</v>
+        <v>6.25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>2.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>3.77</v>
       </c>
       <c r="R17" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="S17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.32</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="X17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AB17" t="n">
         <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.72</v>
+        <v>5.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN17" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X21" t="n">
         <v>2.16</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.29</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,130 +4741,130 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.95</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="X22" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.35</v>
+        <v>5.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.15</v>
       </c>
       <c r="AK22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR22" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AS22" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.39</v>
+        <v>5.87</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.12</v>
+        <v>3.73</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.71</v>
+        <v>2.23</v>
       </c>
       <c r="BB22" t="n">
         <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
         <v>1.25</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.41</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="X23" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
         <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
         <v>1.44</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
         <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AS23" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.19</v>
+        <v>5.44</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.14</v>
+        <v>2.51</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BC23" t="n">
         <v>1.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="BE23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.39</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.45</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>5.7</v>
+        <v>2.16</v>
       </c>
       <c r="S24" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS24" t="n">
         <v>1.83</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U24" t="n">
-        <v>5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W24" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AT24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA24" t="n">
         <v>1.94</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="BB24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,83 +5328,83 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
@@ -5431,34 +5431,34 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="R26" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.25</v>
       </c>
-      <c r="U26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.9</v>
+        <v>4.72</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AM26" t="n">
         <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="AS26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT26" t="n">
         <v>2.36</v>
       </c>
-      <c r="AT26" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AU26" t="n">
-        <v>3.22</v>
+        <v>4.71</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AZ26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.91</v>
       </c>
-      <c r="BA26" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,103 +5726,103 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.45</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z27" t="n">
         <v>4.2</v>
       </c>
-      <c r="R27" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5</v>
-      </c>
       <c r="AA27" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AB27" t="n">
         <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.45</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI27" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AL27" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.69</v>
+        <v>1.53</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.33</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.22</v>
+        <v>4.97</v>
       </c>
       <c r="AV27" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AW27" t="n">
         <v>2.28</v>
@@ -5831,28 +5831,28 @@
         <v>1.87</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.39</v>
+        <v>1.94</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,58 +5923,58 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="S28" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="V28" t="n">
         <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="X28" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z28" t="n">
         <v>4.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AD28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AH28" t="n">
         <v>1.62</v>
@@ -5983,70 +5983,70 @@
         <v>3.7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" t="n">
         <v>1.44</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.44</v>
+        <v>4.39</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="BB28" t="n">
         <v>1.15</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BF28" t="n">
         <v>1.3</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,52 +6792,52 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6989,52 +6989,52 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU33" t="n">
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.25</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2</v>
-      </c>
       <c r="U39" t="n">
-        <v>2.8</v>
+        <v>5.15</v>
       </c>
       <c r="V39" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="X39" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="Z39" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB39" t="n">
         <v>1.04</v>
       </c>
       <c r="AC39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AQ39" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AS39" t="n">
         <v>2.3</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AY39" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="BA39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC39" t="n">
         <v>1.92</v>
       </c>
-      <c r="BB39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD39" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="R41" t="n">
-        <v>4.25</v>
+        <v>2.25</v>
       </c>
       <c r="S41" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>5.15</v>
+        <v>2.8</v>
       </c>
       <c r="V41" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W41" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="X41" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
         <v>1.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI41" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AL41" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AN41" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AS41" t="n">
         <v>2.3</v>
       </c>
       <c r="AT41" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AY41" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10069,25 +10069,25 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="T49" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U49" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="V49" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -10099,40 +10099,40 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AG49" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK49" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10177,13 +10177,13 @@
         <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="BD49" t="n">
         <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="BF49" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10660,25 +10660,25 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T52" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U52" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X52" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -10690,91 +10690,91 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM52" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD52" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AN52" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>1.65</v>
       </c>
       <c r="BF52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10857,19 +10857,19 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="T53" t="n">
         <v>2.08</v>
       </c>
       <c r="U53" t="n">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="V53" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W53" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -10887,22 +10887,22 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -10911,17 +10911,17 @@
         <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN53" t="n">
         <v>1.78</v>
       </c>
-      <c r="AM53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
@@ -10965,13 +10965,13 @@
         <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="BD53" t="n">
         <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BF53" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.43</v>
+        <v>3.76</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="P2" t="n">
-        <v>4.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="T2" t="n">
-        <v>3.01</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.38</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK2" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.76</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>4.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="U3" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.37</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
         <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="S4" t="n">
         <v>1.25</v>
@@ -1082,10 +1082,10 @@
         <v>4.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
         <v>2.3</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>12.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>3.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>9.4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="P6" t="n">
-        <v>5.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.25</v>
+        <v>1.04</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="O7" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>5.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.04</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>12.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.52</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.25</v>
+        <v>2.99</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.97</v>
+        <v>3.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2159,31 +2159,31 @@
         <v>2.43</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="Q11" t="n">
         <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="S11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
@@ -2192,28 +2192,28 @@
         <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
         <v>1.85</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="O15" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P15" t="n">
-        <v>6.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="R15" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S15" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
         <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.45</v>
+        <v>5.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE15" t="n">
         <v>1.22</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.69</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.26</v>
+        <v>1.39</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>4.45</v>
       </c>
       <c r="P16" t="n">
-        <v>3.04</v>
+        <v>5.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="W16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.06</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>1.88</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,17 +3106,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>4.45</v>
+        <v>4.68</v>
       </c>
       <c r="P18" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q18" t="n">
         <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.88</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3583,68 +3583,68 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T21" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="U21" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="P22" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
         <v>1.22</v>
@@ -3926,31 +3926,31 @@
         <v>3.58</v>
       </c>
       <c r="U22" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
         <v>1.63</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AD22" t="n">
         <v>1.62</v>
@@ -3959,10 +3959,10 @@
         <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.73</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P24" t="n">
-        <v>3.35</v>
+        <v>2.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.32</v>
+        <v>3.03</v>
       </c>
       <c r="R24" t="n">
         <v>2.5</v>
       </c>
       <c r="S24" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T24" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="U24" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.72</v>
+        <v>5.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T25" t="n">
-        <v>4.15</v>
+        <v>3.58</v>
       </c>
       <c r="U25" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="V25" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.19</v>
+        <v>3.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="O27" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="S27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.25</v>
       </c>
-      <c r="T27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="AK27" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.26</v>
       </c>
       <c r="O28" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S28" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="U28" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,80 +5654,80 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>1.34</v>
       </c>
       <c r="O33" t="n">
-        <v>3.34</v>
+        <v>4.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2.42</v>
+        <v>7.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>1.78</v>
       </c>
       <c r="R33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
         <v>2.1</v>
       </c>
-      <c r="S33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.53</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.06</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK33" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,19 +5813,19 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5834,10 +5834,10 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -5846,31 +5846,31 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="O38" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q38" t="n">
         <v>2.3</v>
@@ -6464,7 +6464,7 @@
         <v>2.5</v>
       </c>
       <c r="S38" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T38" t="n">
         <v>3.34</v>
@@ -6491,7 +6491,7 @@
         <v>1.57</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC38" t="n">
         <v>2.45</v>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T39" t="n">
         <v>3.1</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.62</v>
-      </c>
       <c r="U39" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
         <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AB39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF39" t="n">
         <v>1.71</v>
       </c>
-      <c r="AC39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6770,10 +6770,10 @@
         <v>2.31</v>
       </c>
       <c r="O40" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.53</v>
+        <v>3.09</v>
       </c>
       <c r="Q40" t="n">
         <v>3.3</v>
@@ -6806,10 +6806,10 @@
         <v>2.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>3.75</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P41" t="n">
-        <v>4.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T41" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="U41" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="V41" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
         <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AG41" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>7.55</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>4.31</v>
       </c>
       <c r="P42" t="n">
-        <v>2.71</v>
+        <v>1.33</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.1</v>
+        <v>7.56</v>
       </c>
       <c r="R42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB42" t="n">
         <v>2</v>
       </c>
-      <c r="S42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC42" t="n">
-        <v>3.44</v>
+        <v>2.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>7.55</v>
+        <v>2.4</v>
       </c>
       <c r="O43" t="n">
-        <v>4.31</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="Q43" t="n">
-        <v>7.56</v>
+        <v>3.1</v>
       </c>
       <c r="R43" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T43" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z43" t="n">
         <v>3.2</v>
       </c>
-      <c r="U43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y43" t="n">
+      <c r="AA43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z43" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE43" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF43" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="P45" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q45" t="n">
         <v>2.75</v>
@@ -7577,16 +7577,16 @@
         <v>1.95</v>
       </c>
       <c r="S45" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T45" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U45" t="n">
         <v>3.25</v>
       </c>
       <c r="V45" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
@@ -7595,19 +7595,19 @@
         <v>1.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z45" t="n">
         <v>2.49</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AD45" t="n">
         <v>1.15</v>
@@ -7616,10 +7616,10 @@
         <v>1.05</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8207,22 +8207,22 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R49" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -8231,47 +8231,47 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK49" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V50" t="n">
         <v>1.4</v>
       </c>
-      <c r="O50" t="n">
-        <v>4</v>
-      </c>
-      <c r="P50" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R50" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U50" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W50" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z50" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK50" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.43</v>
+        <v>1.85</v>
       </c>
       <c r="R51" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S51" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T51" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y51" t="n">
         <v>1.38</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8684,16 +8684,16 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -8708,31 +8708,31 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8843,16 +8843,16 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.76</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>4.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="U2" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.37</v>
+        <v>1.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>4.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="T3" t="n">
-        <v>3.02</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.38</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK3" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>12.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U5" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.25</v>
+        <v>2.99</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.97</v>
+        <v>3.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>5.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.04</v>
+        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="P7" t="n">
-        <v>5.97</v>
+        <v>12.2</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.95</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.99</v>
+        <v>5.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.08</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.37</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T12" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
         <v>1.85</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O14" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
         <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.85</v>
+        <v>3.41</v>
       </c>
       <c r="P15" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T15" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
-        <v>4.45</v>
+        <v>3.65</v>
       </c>
       <c r="P16" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.83</v>
+        <v>2.91</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T16" t="n">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="U16" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="V16" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>3.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.73</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="U20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AC20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O21" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="P21" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="R21" t="n">
         <v>2.5</v>
       </c>
       <c r="S21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T21" t="n">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="U21" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V21" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.72</v>
+        <v>5.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.41</v>
+        <v>2.94</v>
       </c>
       <c r="O24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>3.68</v>
+        <v>3.15</v>
       </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.13</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>1.38</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>5.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.68</v>
+        <v>2.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,52 +4859,52 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.26</v>
+        <v>2.81</v>
       </c>
       <c r="O28" t="n">
         <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.75</v>
+        <v>3.76</v>
       </c>
       <c r="R28" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T28" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
         <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AD28" t="n">
         <v>1.4</v>
@@ -4913,10 +4913,10 @@
         <v>1.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,61 +5654,61 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>7.55</v>
+        <v>2.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.78</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.6</v>
+        <v>3.12</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG33" t="n">
         <v>2</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,61 +5972,61 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.62</v>
+        <v>1.34</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>7.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>1.78</v>
       </c>
       <c r="R35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
         <v>2.1</v>
       </c>
-      <c r="S35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.2</v>
-      </c>
       <c r="V35" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.12</v>
+        <v>4.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.45</v>
+        <v>2.23</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG35" t="n">
         <v>2</v>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q37" t="n">
         <v>2.05</v>
@@ -6305,10 +6305,10 @@
         <v>2.38</v>
       </c>
       <c r="S37" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T37" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="U37" t="n">
         <v>2.16</v>
@@ -6317,7 +6317,7 @@
         <v>1.58</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>4.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T39" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="U39" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V39" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
         <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.59</v>
+        <v>3.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AG39" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,65 +6767,65 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O40" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P40" t="n">
-        <v>3.09</v>
+        <v>4.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="R40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2</v>
       </c>
-      <c r="S40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U40" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,80 +6926,80 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="O41" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
         <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="T41" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="U41" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="V41" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1.03</v>
       </c>
-      <c r="X41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y41" t="n">
+      <c r="AF41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AK41" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="Q43" t="n">
         <v>3.1</v>
@@ -7289,7 +7289,7 @@
         <v>1.75</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AD43" t="n">
         <v>1.25</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK43" t="n">
         <v>1.5</v>
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="O44" t="n">
         <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O46" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P46" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
         <v>3.2</v>
@@ -7736,16 +7736,16 @@
         <v>2.12</v>
       </c>
       <c r="S46" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T46" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U46" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V46" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W46" t="n">
         <v>1.08</v>
@@ -7760,25 +7760,25 @@
         <v>3.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
         <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE46" t="n">
         <v>1.06</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>1.44</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8207,22 +8207,22 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
         <v>2.55</v>
       </c>
-      <c r="R49" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -8231,31 +8231,31 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8366,10 +8366,10 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -8390,31 +8390,31 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="R51" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S51" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T51" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U51" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK51" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.43</v>
+        <v>1.85</v>
       </c>
       <c r="R52" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S52" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T52" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y52" t="n">
         <v>1.38</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF52" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8843,16 +8843,16 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>3.76</v>
       </c>
       <c r="O2" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="P2" t="n">
-        <v>4.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="T2" t="n">
-        <v>3.02</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.38</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK2" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.76</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>4.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="U3" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.37</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q5" t="n">
         <v>3.3</v>
@@ -1223,10 +1223,10 @@
         <v>2.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1241,13 +1241,13 @@
         <v>2.99</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD5" t="n">
         <v>1.3</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,68 +2470,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>3.16</v>
+        <v>4.15</v>
       </c>
       <c r="U14" t="n">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.64</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK14" t="n">
         <v>1.53</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="O15" t="n">
-        <v>3.41</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.95</v>
+        <v>5.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="U15" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="W15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.06</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z15" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.8</v>
+        <v>1.88</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,19 +3587,19 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.71</v>
+        <v>2.83</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="P20" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
         <v>1.22</v>
@@ -3608,31 +3608,31 @@
         <v>3.58</v>
       </c>
       <c r="U20" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
         <v>1.63</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AD20" t="n">
         <v>1.62</v>
@@ -3641,10 +3641,10 @@
         <v>1.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.84</v>
+        <v>2.94</v>
       </c>
       <c r="O21" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.46</v>
+        <v>2.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.54</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,65 +3905,65 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG22" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.38</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.83</v>
+        <v>2.91</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S26" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T26" t="n">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="U26" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="V26" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,80 +4859,80 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.81</v>
+        <v>1.71</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.13</v>
+        <v>3.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.76</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="U28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2.5</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AC28" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK28" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,61 +5654,61 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2.37</v>
+        <v>7.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>1.78</v>
       </c>
       <c r="R33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
         <v>2.1</v>
       </c>
-      <c r="S33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.2</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.12</v>
+        <v>4.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.45</v>
+        <v>2.23</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG33" t="n">
         <v>2</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,19 +5972,19 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -5993,10 +5993,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -6005,31 +6005,31 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="Q36" t="n">
         <v>3.25</v>
@@ -6146,62 +6146,62 @@
         <v>2.1</v>
       </c>
       <c r="S36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V36" t="n">
         <v>1.37</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.52</v>
+        <v>3.12</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AD36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.3</v>
       </c>
       <c r="AK36" t="n">
         <v>1.4</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
         <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="T39" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="U39" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="V39" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.03</v>
       </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y39" t="n">
+      <c r="AF39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,80 +6926,80 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.27</v>
+        <v>2.87</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
         <v>2</v>
       </c>
       <c r="S41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK41" t="n">
         <v>1.55</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U41" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,80 +7085,80 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>7.55</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
-        <v>4.31</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.33</v>
       </c>
-      <c r="Q42" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AK42" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>7.55</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>4.31</v>
       </c>
       <c r="P43" t="n">
-        <v>2.62</v>
+        <v>1.33</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.1</v>
+        <v>7.56</v>
       </c>
       <c r="R43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB43" t="n">
         <v>2</v>
       </c>
-      <c r="S43" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC43" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.31</v>
+        <v>2.59</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="R49" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U49" t="n">
-        <v>2.55</v>
+        <v>3.02</v>
       </c>
       <c r="V49" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8366,10 +8366,10 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -8390,31 +8390,31 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8525,16 +8525,16 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="R51" t="n">
         <v>2.08</v>
       </c>
       <c r="S51" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T51" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -8549,47 +8549,47 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK51" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.68</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="R52" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S52" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T52" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U52" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK52" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8843,16 +8843,16 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>

--- a/jogos_2026-05-25.xlsx
+++ b/jogos_2026-05-25.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.76</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>4.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="U2" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.37</v>
+        <v>1.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>4.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="T3" t="n">
-        <v>3.02</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.38</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK3" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.47</v>
+        <v>1.18</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="P5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="AC5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.45</v>
+        <v>3.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>9.4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="P6" t="n">
-        <v>5.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.25</v>
+        <v>1.04</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.18</v>
       </c>
-      <c r="O7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z7" t="n">
-        <v>5.25</v>
+        <v>3.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>9.4</v>
+        <v>2.47</v>
       </c>
       <c r="O8" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="V8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.7</v>
       </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1.92</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="R11" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T11" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG11" t="n">
         <v>1.85</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.56</v>
       </c>
-      <c r="O12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
         <v>1.85</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,68 +2470,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>4.68</v>
       </c>
       <c r="P14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R14" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.47</v>
-      </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T14" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>4.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.53</v>
+        <v>2.69</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.38</v>
+        <v>2.81</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>5.9</v>
+        <v>2.13</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>3.76</v>
       </c>
       <c r="R15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.7</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>2.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
-        <v>4.68</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U18" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.69</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="O19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T19" t="n">
-        <v>3.52</v>
+        <v>4.15</v>
       </c>
       <c r="U19" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.1</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4.72</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.94</v>
+        <v>1.86</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="U21" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>4.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
         <v>1.53</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.81</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.13</v>
+        <v>5.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.76</v>
+        <v>1.83</v>
       </c>
       <c r="R22" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.92</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O23" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
         <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U23" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.91</v>
+        <v>2.25</v>
       </c>
       <c r="R26" t="n">
         <v>2.5</v>
       </c>
       <c r="S26" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T26" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="U26" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V26" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF26" t="n">
         <v>1.44</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P27" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="R27" t="n">
         <v>2.5</v>
       </c>
       <c r="S27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T27" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="U27" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="V27" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF27" t="n">
         <v>1.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,19 +5654,19 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5675,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5687,31 +5687,31 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,61 +6131,61 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="P36" t="n">
-        <v>2.37</v>
+        <v>7.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>1.78</v>
       </c>
       <c r="R36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
         <v>2.1</v>
       </c>
-      <c r="S36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.2</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.12</v>
+        <v>4.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.45</v>
+        <v>2.23</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG36" t="n">
         <v>2</v>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,65 +6608,65 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="O39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R39" t="n">
         <v>2.4</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG39" t="n">
         <v>2</v>
       </c>
-      <c r="S39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.67</v>
+        <v>2.87</v>
       </c>
       <c r="O40" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P40" t="n">
-        <v>4.45</v>
+        <v>2.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T40" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="U40" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="V40" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
         <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.59</v>
+        <v>3.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,80 +6926,80 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.87</v>
+        <v>2.27</v>
       </c>
       <c r="O41" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
         <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="T41" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="U41" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="V41" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1.03</v>
       </c>
-      <c r="X41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y41" t="n">
+      <c r="AF41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AK41" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>7.55</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>4.31</v>
       </c>
       <c r="P42" t="n">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>7.56</v>
       </c>
       <c r="R42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB42" t="n">
         <v>2</v>
       </c>
-      <c r="S42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC42" t="n">
-        <v>3.44</v>
+        <v>2.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,80 +7244,80 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>7.55</v>
+        <v>2.37</v>
       </c>
       <c r="O43" t="n">
-        <v>4.31</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43" t="n">
         <v>1.33</v>
       </c>
-      <c r="Q43" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AK43" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        